--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A749ECDE-4091-4F7C-ABBF-57E308866B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732AA075-24A0-4FE7-9A86-15BF42C83C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="15" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="186">
   <si>
     <t>Név</t>
   </si>
@@ -337,6 +337,255 @@
   </si>
   <si>
     <t>Gig6/0</t>
+  </si>
+  <si>
+    <t>172.16.0.4/30</t>
+  </si>
+  <si>
+    <t>172.16.0.8/30</t>
+  </si>
+  <si>
+    <t>172.16.0.12/30</t>
+  </si>
+  <si>
+    <t>172.16.0.16/30</t>
+  </si>
+  <si>
+    <t>172.16.0.20/30</t>
+  </si>
+  <si>
+    <t>172.16.0.24/30</t>
+  </si>
+  <si>
+    <t>172.16.0.28/30</t>
+  </si>
+  <si>
+    <t>172.16.0.32/30</t>
+  </si>
+  <si>
+    <t>172.16.0.36/30</t>
+  </si>
+  <si>
+    <t>172.16.0.40/30</t>
+  </si>
+  <si>
+    <t>172.16.0.44/30</t>
+  </si>
+  <si>
+    <t>172.16.0.48/30</t>
+  </si>
+  <si>
+    <t>172.16.0.52/30</t>
+  </si>
+  <si>
+    <t>172.16.0.56/30</t>
+  </si>
+  <si>
+    <t>172.16.0.60/30</t>
+  </si>
+  <si>
+    <t>172.16.0.64/30</t>
+  </si>
+  <si>
+    <t>172.16.0.68/30</t>
+  </si>
+  <si>
+    <t>172.16.0.72/30</t>
+  </si>
+  <si>
+    <t>172.16.0.76/30</t>
+  </si>
+  <si>
+    <t>172.16.0.80/30</t>
+  </si>
+  <si>
+    <t>172.16.0.84/30</t>
+  </si>
+  <si>
+    <t>172.16.0.88/30</t>
+  </si>
+  <si>
+    <t>172.16.0.92/30</t>
+  </si>
+  <si>
+    <t>172.16.0.96/30</t>
+  </si>
+  <si>
+    <t>172.16.0.100/30</t>
+  </si>
+  <si>
+    <t>172.16.0.104/30</t>
+  </si>
+  <si>
+    <t>172.16.0.108/30</t>
+  </si>
+  <si>
+    <t>172.16.0.1</t>
+  </si>
+  <si>
+    <t>172.16.0.2</t>
+  </si>
+  <si>
+    <t>172.16.0.5</t>
+  </si>
+  <si>
+    <t>172.16.0.6</t>
+  </si>
+  <si>
+    <t>172.16.0.9</t>
+  </si>
+  <si>
+    <t>172.16.0.13</t>
+  </si>
+  <si>
+    <t>172.16.0.17</t>
+  </si>
+  <si>
+    <t>172.16.0.21</t>
+  </si>
+  <si>
+    <t>172.16.0.25</t>
+  </si>
+  <si>
+    <t>172.16.0.10</t>
+  </si>
+  <si>
+    <t>172.16.0.14</t>
+  </si>
+  <si>
+    <t>172.16.0.18</t>
+  </si>
+  <si>
+    <t>172.16.0.22</t>
+  </si>
+  <si>
+    <t>172.16.0.26</t>
+  </si>
+  <si>
+    <t>172.16.0.29</t>
+  </si>
+  <si>
+    <t>172.16.0.30</t>
+  </si>
+  <si>
+    <t>172.16.0.33</t>
+  </si>
+  <si>
+    <t>172.16.0.37</t>
+  </si>
+  <si>
+    <t>172.16.0.41</t>
+  </si>
+  <si>
+    <t>172.16.0.45</t>
+  </si>
+  <si>
+    <t>172.16.0.49</t>
+  </si>
+  <si>
+    <t>172.16.0.34</t>
+  </si>
+  <si>
+    <t>172.16.0.38</t>
+  </si>
+  <si>
+    <t>172.16.0.42</t>
+  </si>
+  <si>
+    <t>172.16.0.46</t>
+  </si>
+  <si>
+    <t>172.16.0.50</t>
+  </si>
+  <si>
+    <t>172.16.0.53</t>
+  </si>
+  <si>
+    <t>172.16.0.54</t>
+  </si>
+  <si>
+    <t>172.16.0.57</t>
+  </si>
+  <si>
+    <t>172.16.0.61</t>
+  </si>
+  <si>
+    <t>172.16.0.65</t>
+  </si>
+  <si>
+    <t>172.16.0.69</t>
+  </si>
+  <si>
+    <t>172.16.0.73</t>
+  </si>
+  <si>
+    <t>172.16.0.77</t>
+  </si>
+  <si>
+    <t>172.16.0.81</t>
+  </si>
+  <si>
+    <t>172.16.0.85</t>
+  </si>
+  <si>
+    <t>172.16.0.89</t>
+  </si>
+  <si>
+    <t>172.16.0.93</t>
+  </si>
+  <si>
+    <t>172.16.0.97</t>
+  </si>
+  <si>
+    <t>172.16.0.101</t>
+  </si>
+  <si>
+    <t>172.16.0.105</t>
+  </si>
+  <si>
+    <t>172.16.0.109</t>
+  </si>
+  <si>
+    <t>172.16.0.58</t>
+  </si>
+  <si>
+    <t>172.16.0.62</t>
+  </si>
+  <si>
+    <t>172.16.0.66</t>
+  </si>
+  <si>
+    <t>172.16.0.70</t>
+  </si>
+  <si>
+    <t>172.16.0.74</t>
+  </si>
+  <si>
+    <t>172.16.0.78</t>
+  </si>
+  <si>
+    <t>172.16.0.82</t>
+  </si>
+  <si>
+    <t>172.16.0.86</t>
+  </si>
+  <si>
+    <t>172.16.0.90</t>
+  </si>
+  <si>
+    <t>172.16.0.94</t>
+  </si>
+  <si>
+    <t>172.16.0.98</t>
+  </si>
+  <si>
+    <t>172.16.0.102</t>
+  </si>
+  <si>
+    <t>172.16.0.106</t>
+  </si>
+  <si>
+    <t>172.16.0.110</t>
   </si>
 </sst>
 </file>
@@ -452,7 +701,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -486,6 +735,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1088,472 +1338,833 @@
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="A1" s="19"/>
+      <c r="B1" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="19" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="19" t="s">
         <v>95</v>
       </c>
+      <c r="D2" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="19" t="s">
         <v>88</v>
       </c>
+      <c r="B3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="19" t="s">
         <v>89</v>
       </c>
+      <c r="B4" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="19" t="s">
         <v>90</v>
       </c>
+      <c r="B5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="19" t="s">
         <v>91</v>
       </c>
+      <c r="B6" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="B7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="19" t="s">
         <v>93</v>
       </c>
+      <c r="B8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="19" t="s">
         <v>94</v>
       </c>
+      <c r="B9" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="11" t="s">
         <v>96</v>
       </c>
+      <c r="F12" s="11" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="11" t="s">
         <v>96</v>
       </c>
+      <c r="F13" s="11" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="11" t="s">
         <v>96</v>
       </c>
+      <c r="F14" s="11" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C15" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="11" t="s">
         <v>96</v>
       </c>
+      <c r="F15" s="11" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="11" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="F16" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D17" t="s">
+      <c r="C17" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="11" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="F17" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C18" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="11" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="F18" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D19" t="s">
+      <c r="C19" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="F19" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
+      <c r="C20" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="F20" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C21" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="F21" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
+      <c r="C22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="F22" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C23" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="F23" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
+      <c r="C24" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="F24" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C25" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="F25" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D26" t="s">
+      <c r="C26" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="F26" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D27" t="s">
+      <c r="C27" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="F27" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D28" t="s">
+      <c r="C28" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="F28" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D29" t="s">
+      <c r="C29" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="F29" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D30" t="s">
+      <c r="C30" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="F30" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D31" t="s">
+      <c r="C31" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="F31" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D32" t="s">
+      <c r="C32" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="F32" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D33" t="s">
+      <c r="C33" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="F33" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D34" t="s">
+      <c r="C34" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="F34" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D35" t="s">
+      <c r="C35" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="F35" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D36" t="s">
+      <c r="C36" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="F36" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D37" t="s">
+      <c r="C37" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="11" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="F37" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D38" t="s">
+      <c r="C38" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="11" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="F38" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D39" t="s">
+      <c r="C39" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="11" t="s">
         <v>102</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732AA075-24A0-4FE7-9A86-15BF42C83C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B64075C-3653-4F16-AD16-C5D85A4BF9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-14400" yWindow="15" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="187">
   <si>
     <t>Név</t>
   </si>
@@ -586,13 +586,16 @@
   </si>
   <si>
     <t>172.16.0.110</t>
+  </si>
+  <si>
+    <t>BGP: 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,8 +620,15 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,8 +683,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -697,11 +737,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -735,7 +786,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1349,827 +1405,831 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="11" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="11" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="19" t="s">
         <v>131</v>
       </c>
+      <c r="G12" s="24" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="21" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="22" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="23" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="8" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="20" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="21" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="22" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="23" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="8" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="20" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="21" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="22" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="23" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="8" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="21" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="22" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="23" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="8" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="22" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="23" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="8" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="23" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="8" t="s">
         <v>185</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B64075C-3653-4F16-AD16-C5D85A4BF9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59BFEF3-6B4F-459B-8470-C425905C2F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14400" yWindow="15" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="188">
   <si>
     <t>Név</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Szaküzlet</t>
   </si>
   <si>
-    <t>192.168.20.0</t>
-  </si>
-  <si>
     <t>Iroda Designer + Marketing + Enigneer</t>
   </si>
   <si>
@@ -144,153 +141,15 @@
     <t>255.255.255.252</t>
   </si>
   <si>
-    <t>OceanData Kft. Belső</t>
-  </si>
-  <si>
-    <t>OceanData Kft. 1.ág</t>
-  </si>
-  <si>
-    <t>10.10.10.0</t>
-  </si>
-  <si>
-    <t>OceanData Kft. 2.ág</t>
-  </si>
-  <si>
-    <t>20.20.20.0</t>
-  </si>
-  <si>
-    <t>OceanData Kft. Edge</t>
-  </si>
-  <si>
-    <t>30.30.30.0</t>
-  </si>
-  <si>
-    <t>255.255.255.224</t>
-  </si>
-  <si>
-    <t>192.168.20.1 HSRP</t>
-  </si>
-  <si>
-    <t>DC01</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>Szerep</t>
-  </si>
-  <si>
-    <t>Windows</t>
-  </si>
-  <si>
-    <t>192.168.20.4</t>
-  </si>
-  <si>
-    <t>Primary AD, DNS</t>
-  </si>
-  <si>
-    <t>DC02</t>
-  </si>
-  <si>
-    <t>192.168.20.5</t>
-  </si>
-  <si>
-    <t>Backup AD, DNS</t>
-  </si>
-  <si>
-    <t>FS01</t>
-  </si>
-  <si>
-    <t>Fileshare</t>
-  </si>
-  <si>
-    <t>SQL01</t>
-  </si>
-  <si>
-    <t>MSSQL</t>
-  </si>
-  <si>
-    <t>192.168.20.1</t>
-  </si>
-  <si>
-    <t>192.168.20.2</t>
-  </si>
-  <si>
-    <t>192.168.20.3</t>
-  </si>
-  <si>
-    <t>192.168.20.6</t>
-  </si>
-  <si>
-    <t>192.168.20.7</t>
-  </si>
-  <si>
-    <t>192.168.20.8</t>
-  </si>
-  <si>
-    <t>192.168.20.9</t>
-  </si>
-  <si>
-    <t>192.168.20.10</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>HSRP virtual IP</t>
-  </si>
-  <si>
-    <t>MSSQL listener IP</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>Apache</t>
-  </si>
-  <si>
-    <t>SQL02</t>
-  </si>
-  <si>
-    <t>Linux</t>
-  </si>
-  <si>
-    <t>WEB01</t>
-  </si>
-  <si>
-    <t>BU01</t>
-  </si>
-  <si>
-    <t>192.168.20.20</t>
-  </si>
-  <si>
-    <t>Gateway R</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>MSSQL Heartbeat</t>
   </si>
   <si>
     <t>40.40.40.0</t>
   </si>
   <si>
-    <t>Megjegyzés</t>
-  </si>
-  <si>
-    <t>40.40.40.1 heartbeat</t>
-  </si>
-  <si>
-    <t>40.40.40.2 heartbeat</t>
-  </si>
-  <si>
-    <t>192.168.20.19</t>
-  </si>
-  <si>
-    <t>MSSQL Cluster IP</t>
-  </si>
-  <si>
     <t>ISP1</t>
   </si>
   <si>
@@ -588,7 +447,151 @@
     <t>172.16.0.110</t>
   </si>
   <si>
-    <t>BGP: 10</t>
+    <t>ISP - LAN -&gt; eBGP</t>
+  </si>
+  <si>
+    <t>ISP routerek közt OSPF</t>
+  </si>
+  <si>
+    <t>(IS-IS lett volna, de az nincs)</t>
+  </si>
+  <si>
+    <t>AD DNS</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Fa0</t>
+  </si>
+  <si>
+    <t>Fa1</t>
+  </si>
+  <si>
+    <t>Linux FTP</t>
+  </si>
+  <si>
+    <t>SQL BACKUP</t>
+  </si>
+  <si>
+    <t>BACKUP SERVER1</t>
+  </si>
+  <si>
+    <t>LS1</t>
+  </si>
+  <si>
+    <t>LS2</t>
+  </si>
+  <si>
+    <t>LS3</t>
+  </si>
+  <si>
+    <t>LS4</t>
+  </si>
+  <si>
+    <t>LS5</t>
+  </si>
+  <si>
+    <t>Fa0/1</t>
+  </si>
+  <si>
+    <t>Fa0/2</t>
+  </si>
+  <si>
+    <t>Fa0/3</t>
+  </si>
+  <si>
+    <t>Fa0/4</t>
+  </si>
+  <si>
+    <t>Fa0/5</t>
+  </si>
+  <si>
+    <t>MLS1</t>
+  </si>
+  <si>
+    <t>MLS2</t>
+  </si>
+  <si>
+    <t>MLS3</t>
+  </si>
+  <si>
+    <t>192.168.10.2</t>
+  </si>
+  <si>
+    <t>192.168.10.3</t>
+  </si>
+  <si>
+    <t>192.168.10.4</t>
+  </si>
+  <si>
+    <t>192.168.10.5</t>
+  </si>
+  <si>
+    <t>192.168.10.6</t>
+  </si>
+  <si>
+    <t>192.168.10.7</t>
+  </si>
+  <si>
+    <t>192.168.10.8</t>
+  </si>
+  <si>
+    <t>192.168.10.9</t>
+  </si>
+  <si>
+    <t>192.168.10.10</t>
+  </si>
+  <si>
+    <t>192.168.10.11</t>
+  </si>
+  <si>
+    <t>192.168.10.12</t>
+  </si>
+  <si>
+    <t>192.168.10.13</t>
+  </si>
+  <si>
+    <t>192.168.10.14</t>
+  </si>
+  <si>
+    <t>192.168.10.15</t>
+  </si>
+  <si>
+    <t>192.168.10.16</t>
+  </si>
+  <si>
+    <t>HSRP route: 192.168.10.1</t>
+  </si>
+  <si>
+    <t>192.168.10.20</t>
+  </si>
+  <si>
+    <t>192.168.10.21</t>
+  </si>
+  <si>
+    <t>192.168.10.22</t>
+  </si>
+  <si>
+    <t>192.168.10.23</t>
+  </si>
+  <si>
+    <t>192.168.10.24</t>
+  </si>
+  <si>
+    <t>192.168.10.25</t>
+  </si>
+  <si>
+    <t>192.168.10.26</t>
+  </si>
+  <si>
+    <t>192.168.10.27</t>
+  </si>
+  <si>
+    <t>192.168.10.28</t>
+  </si>
+  <si>
+    <t>192.168.10.29</t>
   </si>
 </sst>
 </file>
@@ -628,7 +631,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -713,6 +716,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -741,9 +756,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -752,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -791,7 +804,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1135,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1200,7 +1224,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>21</v>
@@ -1229,83 +1253,51 @@
       <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>68</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>68</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="16"/>
       <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>68</v>
-      </c>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>68</v>
       </c>
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1330,24 +1322,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -1358,10 +1350,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -1372,16 +1364,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE1BEBB-5344-4140-AC04-666DF37572D0}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -1400,830 +1392,839 @@
     <col min="5" max="5" width="14.42578125" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="24"/>
+      <c r="K12" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D14" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D15" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="D16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>144</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2235,203 +2236,450 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D6D1D5-74AF-4AB6-A0A1-6D17E92BA017}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A2:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="E3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
+        <v>143</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
+        <v>143</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
+        <v>146</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="E7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
+        <v>146</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
+        <v>147</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
+        <v>147</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
+        <v>148</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>68</v>
+        <v>153</v>
+      </c>
+      <c r="E11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>148</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
+        <v>153</v>
+      </c>
+      <c r="E12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="G13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FEAB69-03AF-4D5A-A087-2A9A2C07DC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC12B49-0CCE-4EFC-B9B1-582AE0DFC54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Telephelyek" sheetId="1" r:id="rId1"/>
-    <sheet name="ISP Full Mesh" sheetId="4" r:id="rId2"/>
-    <sheet name="ISP-telephelyek" sheetId="7" r:id="rId3"/>
-    <sheet name="GRE over IPSec" sheetId="10" r:id="rId4"/>
-    <sheet name="OceanData" sheetId="8" r:id="rId5"/>
-    <sheet name="PAT" sheetId="9" r:id="rId6"/>
+    <sheet name="Iroda Címzés" sheetId="11" r:id="rId2"/>
+    <sheet name="Iroda Kapcsolatok" sheetId="12" r:id="rId3"/>
+    <sheet name="ISP Full Mesh" sheetId="4" r:id="rId4"/>
+    <sheet name="ISP-telephelyek" sheetId="7" r:id="rId5"/>
+    <sheet name="GRE over IPSec" sheetId="10" r:id="rId6"/>
+    <sheet name="OceanData" sheetId="8" r:id="rId7"/>
+    <sheet name="PAT" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="216">
   <si>
     <t>Név</t>
   </si>
@@ -582,6 +584,111 @@
   </si>
   <si>
     <t>100.64.0.23</t>
+  </si>
+  <si>
+    <t>Eszköznév</t>
+  </si>
+  <si>
+    <t>Interfész</t>
+  </si>
+  <si>
+    <t>DNS szerver</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/1.1</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/1.2</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/1.3</t>
+  </si>
+  <si>
+    <t>Serial0/1/0</t>
+  </si>
+  <si>
+    <t>100.80.0.2</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/1.10</t>
+  </si>
+  <si>
+    <t>172.100.0.1</t>
+  </si>
+  <si>
+    <t>172.100.0.5</t>
+  </si>
+  <si>
+    <t>172.100.0.17</t>
+  </si>
+  <si>
+    <t>Vlan1</t>
+  </si>
+  <si>
+    <t>192.168.1.2</t>
+  </si>
+  <si>
+    <t>Vlan10</t>
+  </si>
+  <si>
+    <t>192.168.10.2</t>
+  </si>
+  <si>
+    <t>GyarSwitch1</t>
+  </si>
+  <si>
+    <t>Admin1</t>
+  </si>
+  <si>
+    <t>Admin2</t>
+  </si>
+  <si>
+    <t>Fa0</t>
+  </si>
+  <si>
+    <t>192.168.10.3</t>
+  </si>
+  <si>
+    <t>192.168.10.4</t>
+  </si>
+  <si>
+    <t>PDA1-5</t>
+  </si>
+  <si>
+    <t>Wireless0</t>
+  </si>
+  <si>
+    <t>DHCP: 192.168.3.0</t>
+  </si>
+  <si>
+    <t>Dolgozo1-30</t>
+  </si>
+  <si>
+    <t>DHCP: 192.168.2.0</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
+    <t>GigabitEthernet1/1</t>
+  </si>
+  <si>
+    <t>192.168.1.10</t>
+  </si>
+  <si>
+    <t>GigabitEthernet1/2</t>
+  </si>
+  <si>
+    <t>FactoryServer</t>
+  </si>
+  <si>
+    <t>192.168.200.2</t>
+  </si>
+  <si>
+    <t>Cím</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	255.255.255.192</t>
   </si>
 </sst>
 </file>
@@ -742,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -768,6 +875,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,6 +1337,397 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844CBC94-95C3-4B60-925A-43B302EE196C}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF07D394-E2A6-4629-9749-86C791C90392}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE1BEBB-5344-4140-AC04-666DF37572D0}">
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2078,7 +2579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190F3A59-B50E-49FB-9E89-81920C09DDE4}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2124,7 +2625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53B8207-4E04-4A0B-B1B4-9436DF906978}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2237,7 +2738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D271391-A8EE-41A4-AEE1-16B3367C6D79}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2352,7 +2853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF7C11D-B35F-4E63-B1DE-46E390154830}">
   <dimension ref="A2:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -8,19 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC12B49-0CCE-4EFC-B9B1-582AE0DFC54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DCFC78-6042-4AAB-9B55-CFEB407B64DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="11" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Telephelyek" sheetId="1" r:id="rId1"/>
-    <sheet name="Iroda Címzés" sheetId="11" r:id="rId2"/>
-    <sheet name="Iroda Kapcsolatok" sheetId="12" r:id="rId3"/>
-    <sheet name="ISP Full Mesh" sheetId="4" r:id="rId4"/>
-    <sheet name="ISP-telephelyek" sheetId="7" r:id="rId5"/>
-    <sheet name="GRE over IPSec" sheetId="10" r:id="rId6"/>
-    <sheet name="OceanData" sheetId="8" r:id="rId7"/>
-    <sheet name="PAT" sheetId="9" r:id="rId8"/>
+    <sheet name="OceanData Kapcsolatok" sheetId="17" r:id="rId2"/>
+    <sheet name="OceanData Címzés" sheetId="18" r:id="rId3"/>
+    <sheet name="Szaküzlet Címzés" sheetId="15" r:id="rId4"/>
+    <sheet name="Szaküzlet Kapcsolatok" sheetId="16" r:id="rId5"/>
+    <sheet name="Gyárüzem Címzés" sheetId="11" r:id="rId6"/>
+    <sheet name="Gyárüzem Kapcsolatok" sheetId="14" r:id="rId7"/>
+    <sheet name="Iroda Kapcsolatok" sheetId="12" r:id="rId8"/>
+    <sheet name="Iroda címzés" sheetId="13" r:id="rId9"/>
+    <sheet name="ISP Full Mesh" sheetId="4" r:id="rId10"/>
+    <sheet name="ISP címzés" sheetId="19" r:id="rId11"/>
+    <sheet name="ISP kapcsolatok" sheetId="20" r:id="rId12"/>
+    <sheet name="GRE over IPSec" sheetId="10" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="316">
   <si>
     <t>Név</t>
   </si>
@@ -442,15 +447,6 @@
     <t>192.168.20.4</t>
   </si>
   <si>
-    <t>Helyi cím</t>
-  </si>
-  <si>
-    <t>NAT cím</t>
-  </si>
-  <si>
-    <t>Szerver</t>
-  </si>
-  <si>
     <t>192.168.20.6</t>
   </si>
   <si>
@@ -466,27 +462,6 @@
     <t>100.64.0.17</t>
   </si>
   <si>
-    <t>100.64.0.18</t>
-  </si>
-  <si>
-    <t>100.64.0.19</t>
-  </si>
-  <si>
-    <t>100.64.0.21</t>
-  </si>
-  <si>
-    <t>100.64.0.22</t>
-  </si>
-  <si>
-    <t>Gyárüzem</t>
-  </si>
-  <si>
-    <t>OceanData</t>
-  </si>
-  <si>
-    <t>Iroda</t>
-  </si>
-  <si>
     <t>Maszk</t>
   </si>
   <si>
@@ -502,12 +477,6 @@
     <t>ODR2</t>
   </si>
   <si>
-    <t>100.64.0.0/30</t>
-  </si>
-  <si>
-    <t>100.64.0.4/30</t>
-  </si>
-  <si>
     <t>FactoryRouter</t>
   </si>
   <si>
@@ -583,9 +552,6 @@
     <t>192.168.20.9</t>
   </si>
   <si>
-    <t>100.64.0.23</t>
-  </si>
-  <si>
     <t>Eszköznév</t>
   </si>
   <si>
@@ -689,6 +655,345 @@
   </si>
   <si>
     <t xml:space="preserve">	255.255.255.192</t>
+  </si>
+  <si>
+    <t>Gig0/0/0</t>
+  </si>
+  <si>
+    <t>Gig0/1</t>
+  </si>
+  <si>
+    <t>IRSW01</t>
+  </si>
+  <si>
+    <t>Fa0/1</t>
+  </si>
+  <si>
+    <t>Fa0/2</t>
+  </si>
+  <si>
+    <t>Fa0/3</t>
+  </si>
+  <si>
+    <t>Fa0/4</t>
+  </si>
+  <si>
+    <t>Fa0/5</t>
+  </si>
+  <si>
+    <t>Fa0/6</t>
+  </si>
+  <si>
+    <t>Fa0/7</t>
+  </si>
+  <si>
+    <t>Fa0/8</t>
+  </si>
+  <si>
+    <t>IRSW03</t>
+  </si>
+  <si>
+    <t>Marketing1</t>
+  </si>
+  <si>
+    <t>Marketing2</t>
+  </si>
+  <si>
+    <t>Telepvezető</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Gig7/0</t>
+  </si>
+  <si>
+    <t>IRSW02</t>
+  </si>
+  <si>
+    <t>Designer1</t>
+  </si>
+  <si>
+    <t>Designer2</t>
+  </si>
+  <si>
+    <t>Engineer2</t>
+  </si>
+  <si>
+    <t>Engineer1</t>
+  </si>
+  <si>
+    <t>Management1</t>
+  </si>
+  <si>
+    <t>Management2</t>
+  </si>
+  <si>
+    <t>Management4</t>
+  </si>
+  <si>
+    <t>Management3</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/1.5</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/1.6</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/0</t>
+  </si>
+  <si>
+    <t>100.70.0.2</t>
+  </si>
+  <si>
+    <t>172.100.0.9</t>
+  </si>
+  <si>
+    <t>172.100.0.18</t>
+  </si>
+  <si>
+    <t>Vlan5</t>
+  </si>
+  <si>
+    <t>192.168.5.2</t>
+  </si>
+  <si>
+    <t>Vlan6</t>
+  </si>
+  <si>
+    <t>192.168.6.2</t>
+  </si>
+  <si>
+    <t>192.168.5.3</t>
+  </si>
+  <si>
+    <t>192.168.6.3</t>
+  </si>
+  <si>
+    <t>192.168.5.4</t>
+  </si>
+  <si>
+    <t>192.168.6.4</t>
+  </si>
+  <si>
+    <t>Fa1</t>
+  </si>
+  <si>
+    <t>DHCP (192.168.5.0)</t>
+  </si>
+  <si>
+    <t>DHCP (192.168.6.0)</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::1</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::4</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::5</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::7</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::6</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::3</t>
+  </si>
+  <si>
+    <t>2001:DB8:5::2</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::2</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::3</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::4</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::5</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::6</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::7</t>
+  </si>
+  <si>
+    <t>2001:DB8:6::1</t>
+  </si>
+  <si>
+    <t>Maszk/Prefix</t>
+  </si>
+  <si>
+    <t>/64</t>
+  </si>
+  <si>
+    <t>Se0/1/0</t>
+  </si>
+  <si>
+    <t>Gig0/0/1</t>
+  </si>
+  <si>
+    <t>Se8/0</t>
+  </si>
+  <si>
+    <t>Gig1/1</t>
+  </si>
+  <si>
+    <t>PDA-AP</t>
+  </si>
+  <si>
+    <t>Port0</t>
+  </si>
+  <si>
+    <t>WorkerAP</t>
+  </si>
+  <si>
+    <t>Gig1/2</t>
+  </si>
+  <si>
+    <t>Port1</t>
+  </si>
+  <si>
+    <t>Dolgozo1 - 30</t>
+  </si>
+  <si>
+    <t>PDA1 - 5</t>
+  </si>
+  <si>
+    <t>Boltrouter</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0.10</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/1</t>
+  </si>
+  <si>
+    <t>100.90.0.2</t>
+  </si>
+  <si>
+    <t>DataServer</t>
+  </si>
+  <si>
+    <t>Printer0</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>PCLan</t>
+  </si>
+  <si>
+    <t>DHCP (192.168.10.0)</t>
+  </si>
+  <si>
+    <t>VLAN</t>
+  </si>
+  <si>
+    <t>BoltSwtich</t>
+  </si>
+  <si>
+    <t>BoltRouter</t>
+  </si>
+  <si>
+    <t>Gig0/2</t>
+  </si>
+  <si>
+    <t>BoltSwitch</t>
+  </si>
+  <si>
+    <t>Fa</t>
+  </si>
+  <si>
+    <t>Gig0/7</t>
+  </si>
+  <si>
+    <t>OR2</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/1</t>
+  </si>
+  <si>
+    <t>100.64.0.2</t>
+  </si>
+  <si>
+    <t>172.100.0.6</t>
+  </si>
+  <si>
+    <t>172.100.0.14</t>
+  </si>
+  <si>
+    <t>GigabitEthernet0/0/0.20</t>
+  </si>
+  <si>
+    <t>192.168.20.3</t>
+  </si>
+  <si>
+    <t>192.168.20.2</t>
+  </si>
+  <si>
+    <t>100.64.0.5</t>
+  </si>
+  <si>
+    <t>172.100.0.2</t>
+  </si>
+  <si>
+    <t>172.100.0.10</t>
+  </si>
+  <si>
+    <t>OR1</t>
+  </si>
+  <si>
+    <t>Vlan20</t>
+  </si>
+  <si>
+    <t>192.168.20.10</t>
+  </si>
+  <si>
+    <t>OS1</t>
+  </si>
+  <si>
+    <t>192.168.20.11</t>
+  </si>
+  <si>
+    <t>OS2</t>
+  </si>
+  <si>
+    <t>192.168.20.1</t>
+  </si>
+  <si>
+    <t>40.40.40.1</t>
+  </si>
+  <si>
+    <t>40.40.40.2</t>
+  </si>
+  <si>
+    <t>Gig8/0</t>
+  </si>
+  <si>
+    <t>100.64.0.1</t>
+  </si>
+  <si>
+    <t>100.64.0.6</t>
+  </si>
+  <si>
+    <t>100.90.0.1</t>
+  </si>
+  <si>
+    <t>100.70.0.1</t>
+  </si>
+  <si>
+    <t>Serial8/0</t>
+  </si>
+  <si>
+    <t>100.80.0.1</t>
   </si>
 </sst>
 </file>
@@ -849,7 +1154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -872,13 +1177,15 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1227,7 +1534,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -1272,16 +1579,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E5" s="10"/>
     </row>
@@ -1336,398 +1643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844CBC94-95C3-4B60-925A-43B302EE196C}">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF07D394-E2A6-4629-9749-86C791C90392}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE1BEBB-5344-4140-AC04-666DF37572D0}">
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2579,45 +2495,882 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190F3A59-B50E-49FB-9E89-81920C09DDE4}">
-  <dimension ref="A1:D2"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AD5B96-D4D1-43BD-847F-3D16A9AB706F}">
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
+      <c r="C12" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2625,7 +3378,427 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE898456-C91C-4699-BE00-5A95390DB91D}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53B8207-4E04-4A0B-B1B4-9436DF906978}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2640,97 +3813,97 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="19"/>
+        <v>158</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="18"/>
       <c r="E2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>161</v>
+        <v>142</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="19"/>
+        <v>159</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="18"/>
       <c r="E3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>151</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="19"/>
+        <v>160</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="18"/>
       <c r="E4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>155</v>
-      </c>
-      <c r="B5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2738,113 +3911,1481 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D271391-A8EE-41A4-AEE1-16B3367C6D79}">
-  <dimension ref="A1:D7"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C2F53F-7056-4601-9536-8902CD49B5B1}">
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9F89E3-0E9A-43E8-9779-930E51DDF5FC}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D17" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B18" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B253C64D-7A83-4900-85B9-D990F2027C1E}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D78F80E7-5DAA-4737-A41F-C6B7C9335978}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="E3" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844CBC94-95C3-4B60-925A-43B302EE196C}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B2" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D8" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D9" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>180</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD0E619-B844-4381-B453-E7870BA3199B}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="10">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2854,34 +5395,1114 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF7C11D-B35F-4E63-B1DE-46E390154830}">
-  <dimension ref="A2:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF07D394-E2A6-4629-9749-86C791C90392}">
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>147</v>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="10">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECF48E1-F1AE-4CD3-B09C-CCDB54B8C1F6}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Network/cimzes.xlsx
+++ b/Network/cimzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DCFC78-6042-4AAB-9B55-CFEB407B64DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE35229-F2CC-41B1-A0EF-85B0EDB3924E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="11" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="6" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Telephelyek" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="314">
   <si>
     <t>Név</t>
   </si>
@@ -561,9 +561,6 @@
     <t>DNS szerver</t>
   </si>
   <si>
-    <t>GigabitEthernet0/0/1.1</t>
-  </si>
-  <si>
     <t>GigabitEthernet0/0/1.2</t>
   </si>
   <si>
@@ -637,9 +634,6 @@
   </si>
   <si>
     <t>GigabitEthernet1/1</t>
-  </si>
-  <si>
-    <t>192.168.1.10</t>
   </si>
   <si>
     <t>GigabitEthernet1/2</t>
@@ -1154,7 +1148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1183,8 +1177,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2506,870 +2498,870 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>260</v>
+      <c r="C1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" s="21" t="s">
+      <c r="D25" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="D47" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="C48" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="C49" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="21" t="s">
+      <c r="C50" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="21" t="s">
+      <c r="C51" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="21" t="s">
+      <c r="C52" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="21" t="s">
+      <c r="C53" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="21" t="s">
+      <c r="C54" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="21" t="s">
+      <c r="C55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="21" t="s">
+      <c r="C56" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="21" t="s">
+      <c r="C57" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="21" t="s">
+      <c r="C58" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="21" t="s">
+      <c r="C59" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="21" t="s">
+      <c r="C60" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" s="21" t="s">
+      <c r="C61" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="C47" s="21" t="s">
+      <c r="C62" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B60" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="10" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3388,408 +3380,408 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="10" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3936,22 +3928,22 @@
       <c r="D1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>282</v>
+      <c r="E1" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>25</v>
@@ -3959,16 +3951,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>25</v>
@@ -3976,16 +3968,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>25</v>
@@ -3993,13 +3985,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>37</v>
@@ -4013,13 +4005,13 @@
         <v>127</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E6" s="10">
         <v>20</v>
@@ -4030,13 +4022,13 @@
         <v>128</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E7" s="10">
         <v>20</v>
@@ -4047,13 +4039,13 @@
         <v>129</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E8" s="10">
         <v>20</v>
@@ -4064,13 +4056,13 @@
         <v>166</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E9" s="10">
         <v>20</v>
@@ -4081,13 +4073,13 @@
         <v>130</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E10" s="10">
         <v>20</v>
@@ -4098,13 +4090,13 @@
         <v>131</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E11" s="10">
         <v>20</v>
@@ -4115,7 +4107,7 @@
         <v>129</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>166</v>
@@ -4129,16 +4121,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>305</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>25</v>
@@ -4171,7 +4163,7 @@
         <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>
@@ -4185,13 +4177,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>139</v>
@@ -4205,13 +4197,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>165</v>
@@ -4225,13 +4217,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>158</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>165</v>
@@ -4245,13 +4237,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>160</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>165</v>
@@ -4265,33 +4257,33 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="22" t="s">
+      <c r="E6" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>165</v>
@@ -4305,13 +4297,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>165</v>
@@ -4325,13 +4317,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>159</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>165</v>
@@ -4345,13 +4337,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>139</v>
@@ -4365,13 +4357,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>139</v>
@@ -4388,7 +4380,7 @@
         <v>127</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>132</v>
@@ -4397,7 +4389,7 @@
         <v>139</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>132</v>
@@ -4408,7 +4400,7 @@
         <v>128</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>133</v>
@@ -4417,7 +4409,7 @@
         <v>139</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>132</v>
@@ -4428,7 +4420,7 @@
         <v>129</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>134</v>
@@ -4437,7 +4429,7 @@
         <v>139</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>132</v>
@@ -4448,7 +4440,7 @@
         <v>166</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>167</v>
@@ -4457,7 +4449,7 @@
         <v>139</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>132</v>
@@ -4468,7 +4460,7 @@
         <v>130</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>136</v>
@@ -4477,7 +4469,7 @@
         <v>139</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>132</v>
@@ -4488,7 +4480,7 @@
         <v>131</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>135</v>
@@ -4497,7 +4489,7 @@
         <v>139</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>132</v>
@@ -4508,10 +4500,10 @@
         <v>129</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>165</v>
@@ -4528,10 +4520,10 @@
         <v>166</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>165</v>
@@ -4569,7 +4561,7 @@
         <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>
@@ -4583,16 +4575,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>6</v>
@@ -4603,16 +4595,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>275</v>
-      </c>
       <c r="C3" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>6</v>
@@ -4623,16 +4615,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>279</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>6</v>
@@ -4643,16 +4635,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B5" s="10">
         <v>0</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>6</v>
@@ -4663,16 +4655,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>6</v>
@@ -4712,22 +4704,22 @@
       <c r="D1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>282</v>
+      <c r="E1" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E2" s="10">
         <v>10</v>
@@ -4735,16 +4727,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E3" s="10">
         <v>10</v>
@@ -4752,13 +4744,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D4" s="10">
         <v>0</v>
@@ -4769,13 +4761,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>285</v>
-      </c>
       <c r="C5" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>35</v>
@@ -4786,16 +4778,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>25</v>
@@ -4831,7 +4823,7 @@
         <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>138</v>
@@ -4848,13 +4840,13 @@
         <v>143</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>25</v>
@@ -4868,13 +4860,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>25</v>
@@ -4888,7 +4880,7 @@
         <v>143</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>16</v>
@@ -4908,7 +4900,7 @@
         <v>143</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>6</v>
@@ -4928,10 +4920,10 @@
         <v>143</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>165</v>
@@ -4951,7 +4943,7 @@
         <v>145</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>165</v>
@@ -4971,7 +4963,7 @@
         <v>158</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>165</v>
@@ -4991,7 +4983,7 @@
         <v>161</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>165</v>
@@ -5005,13 +4997,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>15</v>
@@ -5025,13 +5017,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>15</v>
@@ -5045,13 +5037,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>15</v>
@@ -5065,13 +5057,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="C13" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>15</v>
@@ -5085,13 +5077,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>15</v>
@@ -5105,16 +5097,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="D15" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>13</v>
@@ -5125,16 +5117,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="C16" s="10" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>25</v>
@@ -5145,10 +5137,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>164</v>
@@ -5165,13 +5157,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>165</v>
@@ -5214,8 +5206,8 @@
       <c r="D1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>282</v>
+      <c r="E1" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -5223,15 +5215,15 @@
         <v>143</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E2" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5240,30 +5232,30 @@
         <v>143</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E3" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
@@ -5271,16 +5263,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E5" s="10">
         <v>3</v>
@@ -5288,16 +5280,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E6" s="10">
         <v>2</v>
@@ -5305,16 +5297,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="D7" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E7" s="10">
         <v>10</v>
@@ -5322,16 +5314,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="E8" s="10">
         <v>10</v>
@@ -5339,16 +5331,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E9" s="10">
         <v>200</v>
@@ -5356,16 +5348,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>270</v>
-      </c>
       <c r="C10" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E10" s="10">
         <v>2</v>
@@ -5373,16 +5365,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>272</v>
-      </c>
       <c r="D11" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E11" s="10">
         <v>3</v>
@@ -5419,8 +5411,8 @@
       <c r="D1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>282</v>
+      <c r="E1" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -5428,98 +5420,98 @@
         <v>144</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="C4" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E4" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="E5" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E7" s="10">
         <v>6</v>
@@ -5527,16 +5519,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E8" s="10">
         <v>6</v>
@@ -5544,16 +5536,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E9" s="10">
         <v>5</v>
@@ -5561,16 +5553,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E10" s="10">
         <v>5</v>
@@ -5578,101 +5570,101 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>144</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E11" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="21">
+        <v>186</v>
+      </c>
+      <c r="E12" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>222</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="21">
+        <v>186</v>
+      </c>
+      <c r="E13" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E15" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E16" s="10">
         <v>6</v>
@@ -5680,16 +5672,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" s="10">
         <v>6</v>
@@ -5697,16 +5689,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E18" s="10">
         <v>5</v>
@@ -5714,16 +5706,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E19" s="10">
         <v>5</v>
@@ -5731,16 +5723,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E20" s="10">
         <v>5</v>
@@ -5748,16 +5740,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E21" s="10">
         <v>5</v>
@@ -5790,10 +5782,10 @@
         <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -5807,7 +5799,7 @@
         <v>144</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>19</v>
@@ -5827,7 +5819,7 @@
         <v>144</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>21</v>
@@ -5847,10 +5839,10 @@
         <v>144</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>165</v>
@@ -5870,7 +5862,7 @@
         <v>159</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>165</v>
@@ -5890,7 +5882,7 @@
         <v>161</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>165</v>
@@ -5904,13 +5896,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>15</v>
@@ -5924,13 +5916,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>15</v>
@@ -5944,13 +5936,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>15</v>
@@ -5964,13 +5956,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>15</v>
@@ -5984,13 +5976,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>15</v>
@@ -6004,13 +5996,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>15</v>
@@ -6024,13 +6016,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>15</v>
@@ -6044,13 +6036,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>15</v>
@@ -6064,13 +6056,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>15</v>
@@ -6084,13 +6076,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>15</v>
@@ -6104,13 +6096,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>15</v>
@@ -6124,13 +6116,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>15</v>
@@ -6144,13 +6136,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>15</v>
@@ -6164,13 +6156,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>15</v>
@@ -6184,13 +6176,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>15</v>
@@ -6204,13 +6196,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>15</v>
@@ -6224,13 +6216,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>15</v>
@@ -6244,13 +6236,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>15</v>
@@ -6264,206 +6256,206 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6471,13 +6463,13 @@
         <v>144</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>25</v>
@@ -6488,13 +6480,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C39" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>25</v>
